--- a/04_Figures/F04_association/modules/training/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/training/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.112087912087912</v>
+        <v>0.0549450549450549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.390746285420994</v>
+        <v>0.190623212915756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.70283316319677</v>
+        <v>0.852007703632368</v>
       </c>
       <c r="G2" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.120879120879121</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E3" t="n">
-        <v>0.421830743866054</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.680607020062893</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G3" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0989010989010989</v>
+        <v>0.0945054945054945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.344291425054203</v>
+        <v>0.328848450013655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.736585369925317</v>
+        <v>0.747938261141548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.173626373626374</v>
+        <v>-0.0153846153846154</v>
       </c>
       <c r="E5" t="n">
-        <v>0.61073549793191</v>
+        <v>-0.0533001790889026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.552766941142241</v>
+        <v>0.958369789371986</v>
       </c>
       <c r="G5" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.463736263736264</v>
+        <v>0.446153846153846</v>
       </c>
       <c r="E6" t="n">
-        <v>1.81318054513692</v>
+        <v>1.7269248691087</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0948763315088996</v>
+        <v>0.109807127801225</v>
       </c>
       <c r="G6" t="n">
-        <v>0.616696154807848</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.287912087912088</v>
+        <v>0.116483516483516</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.04145523072203</v>
+        <v>0.406276413480895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3181928710258</v>
+        <v>0.691691250233157</v>
       </c>
       <c r="G7" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.125274725274725</v>
+        <v>-0.116483516483516</v>
       </c>
       <c r="E8" t="n">
-        <v>0.437410256409312</v>
+        <v>-0.406276413480895</v>
       </c>
       <c r="F8" t="n">
-        <v>0.669582396544844</v>
+        <v>0.691691250233157</v>
       </c>
       <c r="G8" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0593406593406593</v>
+        <v>0.0197802197802198</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.20592495680455</v>
+        <v>0.0685340998265018</v>
       </c>
       <c r="F9" t="n">
-        <v>0.840301762690683</v>
+        <v>0.946489227408011</v>
       </c>
       <c r="G9" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0857142857142857</v>
+        <v>-0.331868131868132</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.298019780339635</v>
+        <v>-1.21869342040738</v>
       </c>
       <c r="F10" t="n">
-        <v>0.770785031118676</v>
+        <v>0.246377183149612</v>
       </c>
       <c r="G10" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.243956043956044</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.871417274558076</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F11" t="n">
-        <v>0.400624803916119</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G11" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.512087912087912</v>
+        <v>0.0725274725274725</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.06526525006142</v>
+        <v>0.251905950462024</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0611984861564584</v>
+        <v>0.805376313541092</v>
       </c>
       <c r="G12" t="n">
-        <v>0.616696154807848</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0461538461538462</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.160052173656655</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.875502537632114</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.875502537632114</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.204395604395604</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.723317557443421</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.483346223042223</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.875502537632114</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0417582417582418</v>
+        <v>0.134065934065934</v>
       </c>
       <c r="E2" t="n">
-        <v>0.144781078854707</v>
+        <v>0.468648785948378</v>
       </c>
       <c r="F2" t="n">
-        <v>0.887286973189064</v>
+        <v>0.647719527985113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.23956043956044</v>
+        <v>-0.173626373626374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.854750807147626</v>
+        <v>-0.61073549793191</v>
       </c>
       <c r="F3" t="n">
-        <v>0.409429892851733</v>
+        <v>0.552766941142241</v>
       </c>
       <c r="G3" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.16043956043956</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0990147542976674</v>
+        <v>0.563073178275514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.922761376569875</v>
+        <v>0.583752752641341</v>
       </c>
       <c r="G4" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0197802197802198</v>
+        <v>0.0505494505494506</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0685340998265018</v>
+        <v>0.175332585602767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.946489227408011</v>
+        <v>0.863742036179215</v>
       </c>
       <c r="G5" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.331868131868132</v>
+        <v>0.279120879120879</v>
       </c>
       <c r="E6" t="n">
-        <v>1.21869342040738</v>
+        <v>1.00692223194835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.246377183149612</v>
+        <v>0.333845077194554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.134065934065934</v>
+        <v>0.032967032967033</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.468648785948378</v>
+        <v>0.114263261126781</v>
       </c>
       <c r="F7" t="n">
-        <v>0.647719527985113</v>
+        <v>0.910918653071845</v>
       </c>
       <c r="G7" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.138461538461538</v>
+        <v>-0.0769230769230769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.484309802250568</v>
+        <v>-0.267261241912424</v>
       </c>
       <c r="F8" t="n">
-        <v>0.636884991265018</v>
+        <v>0.793805888355453</v>
       </c>
       <c r="G8" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0945054945054945</v>
+        <v>0.0593406593406593</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.328848450013655</v>
+        <v>0.20592495680455</v>
       </c>
       <c r="F9" t="n">
-        <v>0.747938261141548</v>
+        <v>0.840301762690683</v>
       </c>
       <c r="G9" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0461538461538462</v>
+        <v>-0.182417582417582</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.160052173656655</v>
+        <v>-0.642696755708738</v>
       </c>
       <c r="F10" t="n">
-        <v>0.875502537632114</v>
+        <v>0.532508818518694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.213186813186813</v>
+        <v>-0.169230769230769</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.755877303492696</v>
+        <v>-0.594811877479463</v>
       </c>
       <c r="F11" t="n">
-        <v>0.464302820039744</v>
+        <v>0.563017273996211</v>
       </c>
       <c r="G11" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.406593406593407</v>
+        <v>0.0373626373626374</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.54166666666667</v>
+        <v>0.12951840569399</v>
       </c>
       <c r="F12" t="n">
-        <v>0.149101939001513</v>
+        <v>0.899093096973967</v>
       </c>
       <c r="G12" t="n">
-        <v>0.946489227408011</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.169230769230769</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.594811877479463</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.563017273996211</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.946489227408011</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.151648351648352</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.531472035224587</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.604790598452137</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.946489227408011</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0505494505494506</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="E2" t="n">
-        <v>0.175332585602767</v>
+        <v>0.160052173656655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.863742036179215</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G2" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.156043956043956</v>
+        <v>-0.318681318681319</v>
       </c>
       <c r="E3" t="n">
-        <v>0.547255944180659</v>
+        <v>-1.16466802690862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.594234700580851</v>
+        <v>0.266784960811361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.142857142857143</v>
+        <v>0.103296703296703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.359754753325688</v>
       </c>
       <c r="F4" t="n">
-        <v>0.626117476225324</v>
+        <v>0.725282211088945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.120879120879121</v>
+        <v>0.116483516483516</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.421830743866054</v>
+        <v>0.406276413480895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.680607020062893</v>
+        <v>0.691691250233157</v>
       </c>
       <c r="G5" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.446153846153846</v>
+        <v>0.424175824175824</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7269248691087</v>
+        <v>1.62259369258211</v>
       </c>
       <c r="F6" t="n">
-        <v>0.109807127801225</v>
+        <v>0.130637310438111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.713746330707963</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.248351648351648</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.888140849482722</v>
+        <v>0.160052173656655</v>
       </c>
       <c r="F7" t="n">
-        <v>0.391919538938457</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G7" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.032967032967033</v>
+        <v>-0.186813186813187</v>
       </c>
       <c r="E8" t="n">
-        <v>0.114263261126781</v>
+        <v>-0.658736619548309</v>
       </c>
       <c r="F8" t="n">
-        <v>0.910918653071845</v>
+        <v>0.522504012379159</v>
       </c>
       <c r="G8" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0989010989010989</v>
+        <v>-0.0725274725274725</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.344291425054203</v>
+        <v>-0.251905950462024</v>
       </c>
       <c r="F9" t="n">
-        <v>0.736585369925317</v>
+        <v>0.805376313541092</v>
       </c>
       <c r="G9" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0285714285714286</v>
+        <v>-0.265934065934066</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0990147542976674</v>
+        <v>-0.955633835704927</v>
       </c>
       <c r="F10" t="n">
-        <v>0.922761376569875</v>
+        <v>0.358113400364786</v>
       </c>
       <c r="G10" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.358241758241758</v>
+        <v>-0.0637362637362637</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.32920682989838</v>
+        <v>-0.221238721732763</v>
       </c>
       <c r="F11" t="n">
-        <v>0.208498124790767</v>
+        <v>0.828626422928612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.903491874093325</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.52967032967033</v>
+        <v>0.12967032967033</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.16319743410023</v>
+        <v>0.453015938607022</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0514165981378708</v>
+        <v>0.658619276321178</v>
       </c>
       <c r="G12" t="n">
-        <v>0.66841577579232</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0637362637362637</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.221238721732763</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.828626422928612</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.922761376569875</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.301098901098901</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.09379712326548</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.295514465607217</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.922761376569875</v>
+        <v>0.875502537632114</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1487,10 +1343,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0505494505494506</v>
+        <v>0.0505494505494506</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.175332585602767</v>
+        <v>0.175332585602767</v>
       </c>
       <c r="F2" t="n">
         <v>0.863742036179215</v>
@@ -1501,7 +1357,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0549450549450549</v>
+        <v>0.520879120879121</v>
       </c>
       <c r="E3" t="n">
-        <v>0.190623212915756</v>
+        <v>2.11376973320625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.852007703632368</v>
+        <v>0.0561539273437027</v>
       </c>
       <c r="G3" t="n">
-        <v>0.958369789371986</v>
+        <v>0.617693200780729</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1533,13 +1389,13 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0901098901098901</v>
+        <v>0.0945054945054945</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.313424881933839</v>
+        <v>0.328848450013655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.759338837815954</v>
+        <v>0.747938261141548</v>
       </c>
       <c r="G4" t="n">
         <v>0.958369789371986</v>
@@ -1547,7 +1403,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.578021978021978</v>
+        <v>-0.248351648351648</v>
       </c>
       <c r="E5" t="n">
-        <v>2.45376820670907</v>
+        <v>-0.888140849482722</v>
       </c>
       <c r="F5" t="n">
-        <v>0.030383014145237</v>
+        <v>0.391919538938457</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394979183888081</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1579,13 +1435,13 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0373626373626374</v>
+        <v>0.0637362637362637</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12951840569399</v>
+        <v>0.221238721732763</v>
       </c>
       <c r="F6" t="n">
-        <v>0.899093096973967</v>
+        <v>0.828626422928612</v>
       </c>
       <c r="G6" t="n">
         <v>0.958369789371986</v>
@@ -1593,7 +1449,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1602,13 +1458,13 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0373626373626374</v>
+        <v>-0.0153846153846154</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.12951840569399</v>
+        <v>-0.0533001790889026</v>
       </c>
       <c r="F7" t="n">
-        <v>0.899093096973967</v>
+        <v>0.958369789371986</v>
       </c>
       <c r="G7" t="n">
         <v>0.958369789371986</v>
@@ -1616,7 +1472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1625,13 +1481,13 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.30989010989011</v>
+        <v>0.0813186813186813</v>
       </c>
       <c r="E8" t="n">
-        <v>1.12907237530428</v>
+        <v>0.282632210255267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.280933280869258</v>
+        <v>0.782274751244096</v>
       </c>
       <c r="G8" t="n">
         <v>0.958369789371986</v>
@@ -1639,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1648,13 +1504,13 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0637362637362637</v>
+        <v>0.301098901098901</v>
       </c>
       <c r="E9" t="n">
-        <v>0.221238721732763</v>
+        <v>1.09379712326548</v>
       </c>
       <c r="F9" t="n">
-        <v>0.828626422928612</v>
+        <v>0.295514465607217</v>
       </c>
       <c r="G9" t="n">
         <v>0.958369789371986</v>
@@ -1662,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1671,13 +1527,13 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.235164835164835</v>
+        <v>0.0373626373626374</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.838140102702703</v>
+        <v>0.12951840569399</v>
       </c>
       <c r="F10" t="n">
-        <v>0.418333896198592</v>
+        <v>0.899093096973967</v>
       </c>
       <c r="G10" t="n">
         <v>0.958369789371986</v>
@@ -1685,7 +1541,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1694,13 +1550,13 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.257142857142857</v>
+        <v>-0.0505494505494506</v>
       </c>
       <c r="E11" t="n">
-        <v>0.92176480169854</v>
+        <v>-0.175332585602767</v>
       </c>
       <c r="F11" t="n">
-        <v>0.37481190387997</v>
+        <v>0.863742036179215</v>
       </c>
       <c r="G11" t="n">
         <v>0.958369789371986</v>
@@ -1708,7 +1564,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1717,61 +1573,15 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0153846153846154</v>
+        <v>-0.116483516483516</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0533001790889026</v>
+        <v>-0.406276413480895</v>
       </c>
       <c r="F12" t="n">
-        <v>0.958369789371986</v>
+        <v>0.691691250233157</v>
       </c>
       <c r="G12" t="n">
-        <v>0.958369789371986</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0505494505494506</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.175332585602767</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.863742036179215</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.958369789371986</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.287912087912088</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.04145523072203</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.3181928710258</v>
-      </c>
-      <c r="G14" t="n">
         <v>0.958369789371986</v>
       </c>
     </row>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0772634461824062</v>
+        <v>-0.143489257195897</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.268450905777255</v>
+        <v>-0.502258804657921</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79291155545467</v>
+        <v>0.624574659876929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.858987518409226</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.337751636168804</v>
+        <v>-0.139074203128331</v>
       </c>
       <c r="E3" t="n">
-        <v>1.24305370449812</v>
+        <v>-0.486494947636061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.237587860212841</v>
+        <v>0.635380141345649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.858987518409226</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.169979581601294</v>
+        <v>0.390732284979597</v>
       </c>
       <c r="E4" t="n">
-        <v>0.597521930556642</v>
+        <v>1.47042903276836</v>
       </c>
       <c r="F4" t="n">
-        <v>0.561265468939588</v>
+        <v>0.167174106289611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.858987518409226</v>
+        <v>0.713583558071973</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0331129055067455</v>
+        <v>0.479033366330918</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.114769406995615</v>
+        <v>1.89043803829291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.910525922192681</v>
+        <v>0.0830866536778713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910525922192681</v>
+        <v>0.713583558071973</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.222960230412086</v>
+        <v>-0.134659149060765</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.79230105983522</v>
+        <v>-0.470760673971169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.443566775254162</v>
+        <v>0.646253491004666</v>
       </c>
       <c r="G6" t="n">
-        <v>0.858987518409226</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.108168824655369</v>
+        <v>-0.0242827973716134</v>
       </c>
       <c r="E7" t="n">
-        <v>0.376919359787956</v>
+        <v>-0.0841428888590603</v>
       </c>
       <c r="F7" t="n">
-        <v>0.712814265313813</v>
+        <v>0.934330263826498</v>
       </c>
       <c r="G7" t="n">
-        <v>0.858987518409226</v>
+        <v>0.934330263826498</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.200884960074256</v>
+        <v>-0.0331129055067455</v>
       </c>
       <c r="E8" t="n">
-        <v>0.710366857397447</v>
+        <v>-0.114769406995615</v>
       </c>
       <c r="F8" t="n">
-        <v>0.491052218723052</v>
+        <v>0.910525922192681</v>
       </c>
       <c r="G8" t="n">
-        <v>0.858987518409226</v>
+        <v>0.934330263826498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.121413986858067</v>
+        <v>0.0551881758445759</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.423725124935532</v>
+        <v>0.191469253719122</v>
       </c>
       <c r="F9" t="n">
-        <v>0.679262298312358</v>
+        <v>0.851359485875606</v>
       </c>
       <c r="G9" t="n">
-        <v>0.858987518409226</v>
+        <v>0.934330263826498</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.452543041925522</v>
+        <v>0.368657014641767</v>
       </c>
       <c r="E10" t="n">
-        <v>1.75796821965203</v>
+        <v>1.37383042898264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.104207007725227</v>
+        <v>0.194613697655993</v>
       </c>
       <c r="G10" t="n">
-        <v>0.858987518409226</v>
+        <v>0.713583558071973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.275940879222879</v>
+        <v>-0.289186041425577</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.994499059084995</v>
+        <v>-1.04648300152506</v>
       </c>
       <c r="F11" t="n">
-        <v>0.339611058042248</v>
+        <v>0.315959934714673</v>
       </c>
       <c r="G11" t="n">
-        <v>0.858987518409226</v>
+        <v>0.868889820465352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.267110771087747</v>
+        <v>0.245035500749917</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.960186428446284</v>
+        <v>0.87551884796786</v>
       </c>
       <c r="F12" t="n">
-        <v>0.355909664957315</v>
+        <v>0.398477714922128</v>
       </c>
       <c r="G12" t="n">
-        <v>0.858987518409226</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.289186041425577</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.04648300152506</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.315959934714673</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.858987518409226</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0949236624526705</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.330316739642975</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.74685613940133</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.858987518409226</v>
+        <v>0.876650972828681</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.236915499533081</v>
+        <v>-0.404960214318173</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.808785738672677</v>
+        <v>-1.46893874127155</v>
       </c>
       <c r="F2" t="n">
-        <v>0.435782488285875</v>
+        <v>0.169858588900401</v>
       </c>
       <c r="G2" t="n">
-        <v>0.809310335388054</v>
+        <v>0.622814825968136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.413224708487931</v>
+        <v>0.0909094358673449</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.50501595720631</v>
+        <v>0.302766193837868</v>
       </c>
       <c r="F3" t="n">
-        <v>0.160481525504564</v>
+        <v>0.767716657539728</v>
       </c>
       <c r="G3" t="n">
-        <v>0.521564957889834</v>
+        <v>0.920781456905966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.030303145289115</v>
+        <v>-0.333334598180265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.100550340209082</v>
+        <v>-1.17260894563959</v>
       </c>
       <c r="F4" t="n">
-        <v>0.921716685469443</v>
+        <v>0.265721285613298</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9501425135439</v>
+        <v>0.729972569590586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.168044714785092</v>
+        <v>-0.0633611219681495</v>
       </c>
       <c r="E5" t="n">
-        <v>0.565381343686788</v>
+        <v>-0.210568169773756</v>
       </c>
       <c r="F5" t="n">
-        <v>0.583162224560326</v>
+        <v>0.837074051732696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.94763861491053</v>
+        <v>0.920781456905966</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.283747633161713</v>
+        <v>0.256199319262518</v>
       </c>
       <c r="E6" t="n">
-        <v>0.981421860119893</v>
+        <v>0.879056422788676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.347477774764846</v>
+        <v>0.39816685614032</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7528685119905</v>
+        <v>0.729972569590586</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.636366051071415</v>
+        <v>-0.280992801771793</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.73609330774691</v>
+        <v>-0.971072316694464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0193662342478975</v>
+        <v>0.352381052360037</v>
       </c>
       <c r="G7" t="n">
-        <v>0.249148311380706</v>
+        <v>0.729972569590586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.311295947060908</v>
+        <v>0.0743804475278277</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.08643345396587</v>
+        <v>0.247377286636928</v>
       </c>
       <c r="F8" t="n">
-        <v>0.300521355395377</v>
+        <v>0.80917280774685</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7528685119905</v>
+        <v>0.920781456905966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0743804475278277</v>
+        <v>-0.220386511193563</v>
       </c>
       <c r="E9" t="n">
-        <v>0.247377286636928</v>
+        <v>-0.749364268031603</v>
       </c>
       <c r="F9" t="n">
-        <v>0.80917280774685</v>
+        <v>0.469360467437088</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9501425135439</v>
+        <v>0.73756644882971</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0192838197294368</v>
+        <v>-0.72176582415892</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0639690896285927</v>
+        <v>-3.45860032793266</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9501425135439</v>
+        <v>0.00534633798793392</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9501425135439</v>
+        <v>0.0588097178672731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0468321336286322</v>
+        <v>0.578514591883104</v>
       </c>
       <c r="E11" t="n">
-        <v>0.155495228836124</v>
+        <v>2.35231288697677</v>
       </c>
       <c r="F11" t="n">
-        <v>0.879247633484673</v>
+        <v>0.0383305094431855</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9501425135439</v>
+        <v>0.21081780193752</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0716256161379081</v>
+        <v>-0.00275483138991954</v>
       </c>
       <c r="E12" t="n">
-        <v>0.238167005296161</v>
+        <v>-0.00913677675106004</v>
       </c>
       <c r="F12" t="n">
-        <v>0.816129936624229</v>
+        <v>0.992873609475608</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9501425135439</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.578514591883104</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.35231288697677</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0383305094431855</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.249148311380706</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.520663132694794</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-2.02262906898504</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0681080388591742</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.295134835056422</v>
+        <v>0.992873609475608</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2501,24 +2219,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.125274725274725</v>
+        <v>0.0725274725274725</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.236915499533081</v>
+        <v>0.256199319262518</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.200884960074256</v>
+        <v>0.143489257195897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.138461538461538</v>
+        <v>0.134065934065934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,33 +2323,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.142857142857143</v>
+        <v>0.116483516483516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0637362637362637</v>
+        <v>0.0813186813186813</v>
       </c>
     </row>
   </sheetData>
